--- a/Config/Excels/Local/L-Localization-UI.xlsx
+++ b/Config/Excels/Local/L-Localization-UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17810"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="ui" sheetId="11" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024">
   <si>
     <t>##var</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
   </si>
   <si>
     <t>##</t>
@@ -3096,12 +3093,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3151,23 +3148,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF161616"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="SimSun"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3185,7 +3169,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3199,8 +3191,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3227,15 +3257,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3250,84 +3298,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3342,19 +3326,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3372,31 +3392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3414,13 +3410,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3432,37 +3494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3472,68 +3510,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3586,31 +3564,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3625,16 +3588,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3657,17 +3620,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3687,13 +3646,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3703,10 +3666,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3715,16 +3678,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3733,119 +3696,119 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3874,31 +3837,22 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4229,17 +4183,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q103"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q100"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5833333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="22.5833333333333" style="3" customWidth="1"/>
     <col min="5" max="17" width="22.5833333333333" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" spans="1:17">
+    <row r="1" ht="18" spans="1:17">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4267,3567 +4222,3504 @@
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
+    <row r="2" ht="18" spans="1:17">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="B2" s="6"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="9" t="s">
-        <v>17</v>
+      <c r="C2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="1:17">
+      <c r="A3" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="5" t="s">
+      <c r="C3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="K3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="L3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="M3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="20" t="s">
+      <c r="O3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="P3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="P5" s="20" t="s">
+      <c r="Q3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" s="20" t="s">
+    </row>
+    <row r="4" ht="28.5" spans="1:17">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="17" t="s">
+      <c r="D4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="G4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="H4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="I4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="L4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="O4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="P4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="Q4" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="Q7" s="16" t="s">
+    </row>
+    <row r="5" ht="18" spans="1:17">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="17" t="s">
+      <c r="D5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="J5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="K5" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="L5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="N5" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="O5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="P5" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="Q5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="Q8" s="16" t="s">
+    </row>
+    <row r="6" ht="18" spans="1:17">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="17" t="s">
+      <c r="D6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E6" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="F6" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="G6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="H6" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="L6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="M6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="N6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="O6" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="P6" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q6" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="Q9" s="16" t="s">
+    </row>
+    <row r="7" ht="18" spans="1:17">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="12" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="17" t="s">
+      <c r="D7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E7" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="G7" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="J7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="K7" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="L7" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="M7" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="N7" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="O7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="P7" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="Q7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="Q10" s="16" t="s">
+    </row>
+    <row r="8" ht="18" spans="1:17">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="17" t="s">
+      <c r="D8" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="G8" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="J8" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="K8" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="L8" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M8" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="N8" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="O8" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="P8" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="Q8" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="Q11" s="16" t="s">
+    </row>
+    <row r="9" ht="18" spans="1:17">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="17" t="s">
+      <c r="D9" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="F9" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="G9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="I9" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="J9" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="K9" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="L9" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="M9" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="N9" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="O9" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="P9" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="Q9" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="Q12" s="16" t="s">
+    </row>
+    <row r="10" ht="18" spans="1:17">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="17" t="s">
+      <c r="D10" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="E10" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G10" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="J10" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="K10" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="L10" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M10" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="N10" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="O10" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="P10" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="P13" s="16" t="s">
+      <c r="Q10" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="Q13" s="16" t="s">
+    </row>
+    <row r="11" ht="18" spans="1:17">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="17" t="s">
+      <c r="D11" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>142</v>
       </c>
+      <c r="F11" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:17">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:17">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="3:17">
+      <c r="C14" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>186</v>
+      </c>
       <c r="E14" s="16" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>157</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17">
+      <c r="C15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c r="Q15" s="16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>172</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17">
+      <c r="C16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="3:17">
-      <c r="C17" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="J17" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="O17" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>200</v>
+      <c r="C17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="3:17">
       <c r="C18" s="2" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="O18" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>215</v>
+        <v>246</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="3:17">
       <c r="C19" s="2" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="P19" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q19" s="19" t="s">
-        <v>230</v>
+        <v>261</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="3:17">
       <c r="C20" s="2" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="N20" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="O20" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>245</v>
+        <v>276</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="3:17">
       <c r="C21" s="2" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N21" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="P21" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q21" s="19" t="s">
-        <v>260</v>
+        <v>291</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="3:17">
       <c r="C22" s="2" t="s">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="M22" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="N22" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="P22" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q22" s="19" t="s">
-        <v>275</v>
+        <v>305</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="3:17">
       <c r="C23" s="2" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="N23" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="O23" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="P23" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q23" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17">
+        <v>319</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" ht="28.5" spans="3:17">
       <c r="C24" s="2" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="N24" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="O24" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="P24" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q24" s="19" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17">
+        <v>333</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="O24" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" ht="28.5" spans="3:17">
       <c r="C25" s="2" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>314</v>
-      </c>
-      <c r="N25" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="P25" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q25" s="19" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="26" spans="3:17">
+        <v>348</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="O25" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" ht="28.5" spans="3:17">
       <c r="C26" s="2" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="K26" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="N26" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="O26" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="P26" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q26" s="19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="27" ht="28" spans="3:17">
+        <v>363</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="27" ht="28.5" spans="3:17">
       <c r="C27" s="2" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="N27" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="P27" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q27" s="19" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="28" ht="28" spans="3:17">
+        <v>378</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q27" s="16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17">
       <c r="C28" s="2" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="M28" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="N28" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="O28" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q28" s="19" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="29" ht="28" spans="3:17">
+        <v>393</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q28" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29" ht="28.5" spans="3:17">
       <c r="C29" s="2" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="M29" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="N29" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="P29" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17">
+        <v>408</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="O29" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="30" ht="28.5" spans="3:17">
       <c r="C30" s="2" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="M30" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="N30" s="19" t="s">
-        <v>389</v>
-      </c>
-      <c r="O30" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="P30" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="31" spans="3:17">
+        <v>423</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="31" ht="29.25" spans="3:17">
       <c r="C31" s="2" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="K31" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="L31" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="N31" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="O31" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="P31" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q31" s="19" t="s">
-        <v>407</v>
+        <v>438</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="O31" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="P31" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q31" s="16" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="3:17">
       <c r="C32" s="2" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="L32" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="M32" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="N32" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="O32" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="P32" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="33" ht="28" spans="3:17">
+        <v>453</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="O32" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="P32" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q32" s="16" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17">
       <c r="C33" s="2" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>425</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>426</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="L33" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="N33" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="O33" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="P33" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q33" s="19" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="34" ht="28" spans="3:17">
+        <v>468</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="O33" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="P33" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q33" s="16" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17">
       <c r="C34" s="2" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="L34" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="M34" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="N34" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="O34" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>452</v>
+        <v>483</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="O34" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="P34" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q34" s="16" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="2" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="J35" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="L35" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="M35" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="N35" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="O35" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="P35" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q35" s="19" t="s">
-        <v>467</v>
+        <v>496</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="2" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>475</v>
-      </c>
-      <c r="K36" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="L36" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="N36" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="O36" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q36" s="19" t="s">
-        <v>482</v>
+        <v>498</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="O36" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="P36" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q36" s="16" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="2" t="s">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="L37" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="M37" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="N37" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="O37" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="P37" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q37" s="19" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="38" spans="3:17">
+        <v>513</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="O37" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q37" s="16" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="38" ht="28.5" spans="3:17">
       <c r="C38" s="2" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>497</v>
+        <v>527</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="O38" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q38" s="16" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="2" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>500</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="K39" s="19" t="s">
-        <v>506</v>
-      </c>
-      <c r="L39" s="19" t="s">
-        <v>507</v>
-      </c>
-      <c r="M39" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="N39" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="O39" s="19" t="s">
-        <v>510</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q39" s="19" t="s">
-        <v>512</v>
+        <v>541</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="O39" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q39" s="16" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="40" spans="3:17">
       <c r="C40" s="2" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>515</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="K40" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="L40" s="19" t="s">
-        <v>521</v>
-      </c>
-      <c r="M40" s="19" t="s">
-        <v>522</v>
-      </c>
-      <c r="N40" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="O40" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="P40" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q40" s="19" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="41" ht="28" spans="3:17">
+        <v>555</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="O40" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="P40" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q40" s="16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="41" spans="3:17">
       <c r="C41" s="2" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>528</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>529</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>531</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>533</v>
-      </c>
-      <c r="K41" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="L41" s="19" t="s">
-        <v>535</v>
-      </c>
-      <c r="M41" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="N41" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="O41" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="P41" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q41" s="19" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="42" spans="3:17">
+        <v>569</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="O41" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="P41" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q41" s="16" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="42" ht="29.25" spans="3:17">
       <c r="C42" s="2" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>545</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>547</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="K42" s="19" t="s">
-        <v>549</v>
-      </c>
-      <c r="L42" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="M42" s="19" t="s">
-        <v>551</v>
-      </c>
-      <c r="N42" s="19" t="s">
-        <v>549</v>
-      </c>
-      <c r="O42" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="P42" s="19" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q42" s="19" t="s">
-        <v>554</v>
+        <v>583</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="O42" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="P42" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q42" s="16" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="2" t="s">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>558</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>559</v>
-      </c>
-      <c r="I43" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>561</v>
-      </c>
-      <c r="K43" s="19" t="s">
-        <v>562</v>
-      </c>
-      <c r="L43" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="M43" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="N43" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="O43" s="19" t="s">
-        <v>566</v>
-      </c>
-      <c r="P43" s="19" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q43" s="19" t="s">
-        <v>568</v>
+        <v>598</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="O43" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="P43" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q43" s="16" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="2" t="s">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>571</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="K44" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="L44" s="19" t="s">
-        <v>577</v>
-      </c>
-      <c r="M44" s="19" t="s">
-        <v>578</v>
-      </c>
-      <c r="N44" s="19" t="s">
-        <v>579</v>
-      </c>
-      <c r="O44" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="P44" s="19" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q44" s="19" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="45" ht="28" spans="3:17">
+        <v>612</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>615</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="J44" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="O44" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="P44" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q44" s="16" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="45" spans="3:17">
       <c r="C45" s="2" t="s">
-        <v>583</v>
+        <v>625</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>585</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>586</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>587</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>588</v>
-      </c>
-      <c r="I45" s="19" t="s">
-        <v>589</v>
-      </c>
-      <c r="J45" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="K45" s="19" t="s">
-        <v>591</v>
-      </c>
-      <c r="L45" s="19" t="s">
-        <v>592</v>
-      </c>
-      <c r="M45" s="19" t="s">
-        <v>593</v>
-      </c>
-      <c r="N45" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="O45" s="19" t="s">
-        <v>595</v>
-      </c>
-      <c r="P45" s="19" t="s">
-        <v>596</v>
-      </c>
-      <c r="Q45" s="19" t="s">
-        <v>597</v>
+        <v>626</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>627</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>633</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="O45" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="P45" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="Q45" s="16" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="2" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>600</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>601</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>602</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>603</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>604</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="L46" s="19" t="s">
-        <v>606</v>
-      </c>
-      <c r="M46" s="19" t="s">
-        <v>607</v>
-      </c>
-      <c r="N46" s="19" t="s">
-        <v>608</v>
-      </c>
-      <c r="O46" s="19" t="s">
-        <v>609</v>
-      </c>
-      <c r="P46" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q46" s="19" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="47" spans="3:17">
+        <v>641</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>642</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="O46" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="P46" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q46" s="16" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="47" ht="28.5" spans="3:17">
       <c r="C47" s="2" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>615</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>616</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>617</v>
-      </c>
-      <c r="I47" s="19" t="s">
-        <v>618</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="K47" s="19" t="s">
-        <v>620</v>
-      </c>
-      <c r="L47" s="19" t="s">
-        <v>621</v>
-      </c>
-      <c r="M47" s="19" t="s">
-        <v>622</v>
-      </c>
-      <c r="N47" s="19" t="s">
-        <v>623</v>
-      </c>
-      <c r="O47" s="19" t="s">
-        <v>624</v>
-      </c>
-      <c r="P47" s="19" t="s">
-        <v>624</v>
-      </c>
-      <c r="Q47" s="19" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="48" spans="3:17">
+        <v>656</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="J47" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>664</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="O47" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="P47" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q47" s="16" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="48" ht="28.5" spans="3:17">
       <c r="C48" s="2" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>628</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>629</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>630</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>631</v>
-      </c>
-      <c r="I48" s="19" t="s">
-        <v>632</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="K48" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="L48" s="19" t="s">
-        <v>635</v>
-      </c>
-      <c r="M48" s="19" t="s">
-        <v>636</v>
-      </c>
-      <c r="N48" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="O48" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="P48" s="19" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q48" s="19" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17">
+        <v>671</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="O48" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="P48" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q48" s="16" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="49" ht="28.5" spans="3:17">
       <c r="C49" s="2" t="s">
-        <v>641</v>
+        <v>684</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>643</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>645</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>646</v>
-      </c>
-      <c r="I49" s="19" t="s">
-        <v>647</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>648</v>
-      </c>
-      <c r="K49" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="L49" s="19" t="s">
-        <v>650</v>
-      </c>
-      <c r="M49" s="19" t="s">
-        <v>651</v>
-      </c>
-      <c r="N49" s="19" t="s">
-        <v>652</v>
-      </c>
-      <c r="O49" s="19" t="s">
-        <v>653</v>
-      </c>
-      <c r="P49" s="19" t="s">
-        <v>654</v>
-      </c>
-      <c r="Q49" s="19" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="50" ht="28" spans="3:17">
+        <v>685</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="O49" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="P49" s="16" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q49" s="16" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="50" ht="28.5" spans="3:17">
       <c r="C50" s="2" t="s">
-        <v>656</v>
+        <v>699</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>660</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>661</v>
-      </c>
-      <c r="I50" s="19" t="s">
-        <v>662</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>663</v>
-      </c>
-      <c r="K50" s="19" t="s">
-        <v>664</v>
-      </c>
-      <c r="L50" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="M50" s="19" t="s">
-        <v>666</v>
-      </c>
-      <c r="N50" s="19" t="s">
-        <v>667</v>
-      </c>
-      <c r="O50" s="19" t="s">
-        <v>668</v>
-      </c>
-      <c r="P50" s="19" t="s">
-        <v>669</v>
-      </c>
-      <c r="Q50" s="19" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="51" ht="28" spans="3:17">
+        <v>700</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>705</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>708</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>709</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>710</v>
+      </c>
+      <c r="O50" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="P50" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q50" s="16" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="51" ht="34.5" spans="3:17">
       <c r="C51" s="2" t="s">
-        <v>671</v>
+        <v>714</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>672</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>673</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>674</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>675</v>
-      </c>
-      <c r="I51" s="19" t="s">
-        <v>676</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>678</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>679</v>
-      </c>
-      <c r="M51" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="N51" s="19" t="s">
-        <v>681</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>682</v>
-      </c>
-      <c r="P51" s="19" t="s">
-        <v>683</v>
-      </c>
-      <c r="Q51" s="19" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="52" ht="28" spans="3:17">
+        <v>715</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>722</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>724</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="O51" s="16" t="s">
+        <v>726</v>
+      </c>
+      <c r="P51" s="16" t="s">
+        <v>726</v>
+      </c>
+      <c r="Q51" s="16" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17">
       <c r="C52" s="2" t="s">
-        <v>685</v>
+        <v>728</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>687</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>688</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>689</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>690</v>
-      </c>
-      <c r="I52" s="19" t="s">
-        <v>691</v>
-      </c>
-      <c r="J52" s="19" t="s">
-        <v>692</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>693</v>
-      </c>
-      <c r="L52" s="19" t="s">
-        <v>694</v>
-      </c>
-      <c r="M52" s="19" t="s">
-        <v>695</v>
-      </c>
-      <c r="N52" s="19" t="s">
-        <v>696</v>
-      </c>
-      <c r="O52" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="P52" s="19" t="s">
-        <v>698</v>
-      </c>
-      <c r="Q52" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="53" ht="28" spans="3:17">
+        <v>729</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="J52" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>736</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>737</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>738</v>
+      </c>
+      <c r="N52" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="O52" s="16" t="s">
+        <v>740</v>
+      </c>
+      <c r="P52" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q52" s="16" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17">
       <c r="C53" s="2" t="s">
-        <v>700</v>
+        <v>743</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>702</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>703</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>704</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>705</v>
-      </c>
-      <c r="I53" s="19" t="s">
-        <v>706</v>
-      </c>
-      <c r="J53" s="19" t="s">
-        <v>707</v>
-      </c>
-      <c r="K53" s="19" t="s">
-        <v>708</v>
-      </c>
-      <c r="L53" s="19" t="s">
-        <v>709</v>
-      </c>
-      <c r="M53" s="19" t="s">
-        <v>710</v>
-      </c>
-      <c r="N53" s="19" t="s">
-        <v>711</v>
-      </c>
-      <c r="O53" s="19" t="s">
-        <v>712</v>
-      </c>
-      <c r="P53" s="19" t="s">
-        <v>713</v>
-      </c>
-      <c r="Q53" s="19" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="54" ht="33" spans="3:17">
+        <v>744</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>746</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>747</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="J53" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>752</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="O53" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="P53" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="Q53" s="16" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17">
       <c r="C54" s="2" t="s">
-        <v>715</v>
+        <v>757</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>718</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>719</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>720</v>
-      </c>
-      <c r="I54" s="19" t="s">
-        <v>721</v>
-      </c>
-      <c r="J54" s="19" t="s">
-        <v>722</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>723</v>
-      </c>
-      <c r="L54" s="19" t="s">
-        <v>724</v>
-      </c>
-      <c r="M54" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="N54" s="19" t="s">
-        <v>726</v>
-      </c>
-      <c r="O54" s="19" t="s">
-        <v>727</v>
-      </c>
-      <c r="P54" s="19" t="s">
-        <v>727</v>
-      </c>
-      <c r="Q54" s="19" t="s">
-        <v>728</v>
+        <v>758</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>760</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="O54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="P54" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q54" s="16" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="2" t="s">
-        <v>729</v>
+        <v>765</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>731</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>732</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>733</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>734</v>
-      </c>
-      <c r="I55" s="19" t="s">
-        <v>735</v>
-      </c>
-      <c r="J55" s="19" t="s">
-        <v>736</v>
-      </c>
-      <c r="K55" s="19" t="s">
-        <v>737</v>
-      </c>
-      <c r="L55" s="19" t="s">
-        <v>738</v>
-      </c>
-      <c r="M55" s="19" t="s">
-        <v>739</v>
-      </c>
-      <c r="N55" s="19" t="s">
-        <v>740</v>
-      </c>
-      <c r="O55" s="19" t="s">
-        <v>741</v>
-      </c>
-      <c r="P55" s="19" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q55" s="19" t="s">
-        <v>743</v>
+        <v>766</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>772</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="O55" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="P55" s="16" t="s">
+        <v>777</v>
+      </c>
+      <c r="Q55" s="16" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="2" t="s">
-        <v>744</v>
+        <v>779</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>745</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>746</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>747</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>748</v>
-      </c>
-      <c r="I56" s="19" t="s">
-        <v>749</v>
-      </c>
-      <c r="J56" s="19" t="s">
-        <v>750</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>751</v>
-      </c>
-      <c r="L56" s="19" t="s">
-        <v>752</v>
-      </c>
-      <c r="M56" s="19" t="s">
-        <v>753</v>
-      </c>
-      <c r="N56" s="19" t="s">
-        <v>754</v>
-      </c>
-      <c r="O56" s="19" t="s">
-        <v>755</v>
-      </c>
-      <c r="P56" s="19" t="s">
-        <v>756</v>
-      </c>
-      <c r="Q56" s="19" t="s">
-        <v>757</v>
+        <v>780</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="I56" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="O56" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="P56" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q56" s="16" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="2" t="s">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>759</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>759</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>761</v>
-      </c>
-      <c r="I57" s="19" t="s">
-        <v>762</v>
-      </c>
-      <c r="J57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="L57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="M57" s="19" t="s">
-        <v>763</v>
-      </c>
-      <c r="N57" s="19" t="s">
-        <v>764</v>
-      </c>
-      <c r="O57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="P57" s="19" t="s">
-        <v>760</v>
-      </c>
-      <c r="Q57" s="19" t="s">
-        <v>765</v>
+        <v>793</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="I57" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>802</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="O57" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="P57" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q57" s="16" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="2" t="s">
-        <v>766</v>
+        <v>807</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>767</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>768</v>
-      </c>
-      <c r="G58" s="19" t="s">
-        <v>769</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>770</v>
-      </c>
-      <c r="I58" s="19" t="s">
-        <v>771</v>
-      </c>
-      <c r="J58" s="19" t="s">
-        <v>772</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="L58" s="19" t="s">
-        <v>774</v>
-      </c>
-      <c r="M58" s="19" t="s">
-        <v>775</v>
-      </c>
-      <c r="N58" s="19" t="s">
-        <v>776</v>
-      </c>
-      <c r="O58" s="19" t="s">
-        <v>777</v>
-      </c>
-      <c r="P58" s="19" t="s">
-        <v>778</v>
-      </c>
-      <c r="Q58" s="19" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17">
+        <v>808</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="O58" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="P58" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="Q58" s="16" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="59" ht="34.5" spans="3:17">
       <c r="C59" s="2" t="s">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>781</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>782</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>781</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>783</v>
-      </c>
-      <c r="I59" s="19" t="s">
-        <v>784</v>
-      </c>
-      <c r="J59" s="19" t="s">
-        <v>785</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>786</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>787</v>
-      </c>
-      <c r="M59" s="19" t="s">
-        <v>788</v>
-      </c>
-      <c r="N59" s="19" t="s">
-        <v>789</v>
-      </c>
-      <c r="O59" s="19" t="s">
-        <v>790</v>
-      </c>
-      <c r="P59" s="19" t="s">
-        <v>791</v>
-      </c>
-      <c r="Q59" s="19" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17">
+        <v>822</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="O59" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="P59" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q59" s="16" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="60" ht="34.5" spans="3:17">
       <c r="C60" s="2" t="s">
-        <v>793</v>
+        <v>836</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>795</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>796</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>797</v>
-      </c>
-      <c r="H60" s="19" t="s">
-        <v>798</v>
-      </c>
-      <c r="I60" s="19" t="s">
-        <v>799</v>
-      </c>
-      <c r="J60" s="19" t="s">
-        <v>800</v>
-      </c>
-      <c r="K60" s="19" t="s">
-        <v>801</v>
-      </c>
-      <c r="L60" s="19" t="s">
-        <v>802</v>
-      </c>
-      <c r="M60" s="19" t="s">
-        <v>803</v>
-      </c>
-      <c r="N60" s="19" t="s">
-        <v>804</v>
-      </c>
-      <c r="O60" s="19" t="s">
-        <v>805</v>
-      </c>
-      <c r="P60" s="19" t="s">
-        <v>806</v>
-      </c>
-      <c r="Q60" s="19" t="s">
-        <v>807</v>
+        <v>837</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>838</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>841</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>842</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="O60" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="P60" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q60" s="16" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="2" t="s">
-        <v>808</v>
+        <v>851</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>810</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>811</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>812</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>813</v>
-      </c>
-      <c r="I61" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="J61" s="19" t="s">
-        <v>811</v>
-      </c>
-      <c r="K61" s="19" t="s">
-        <v>815</v>
-      </c>
-      <c r="L61" s="19" t="s">
-        <v>816</v>
-      </c>
-      <c r="M61" s="19" t="s">
-        <v>817</v>
-      </c>
-      <c r="N61" s="19" t="s">
-        <v>818</v>
-      </c>
-      <c r="O61" s="19" t="s">
-        <v>819</v>
-      </c>
-      <c r="P61" s="19" t="s">
-        <v>820</v>
-      </c>
-      <c r="Q61" s="19" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="62" ht="33" spans="3:17">
+        <v>852</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>852</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>853</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>854</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>855</v>
+      </c>
+      <c r="I61" s="16" t="s">
+        <v>856</v>
+      </c>
+      <c r="J61" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>858</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>859</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>861</v>
+      </c>
+      <c r="O61" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="P61" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q61" s="16" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17">
       <c r="C62" s="2" t="s">
-        <v>822</v>
+        <v>865</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>824</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>827</v>
-      </c>
-      <c r="I62" s="19" t="s">
-        <v>828</v>
-      </c>
-      <c r="J62" s="19" t="s">
-        <v>829</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>830</v>
-      </c>
-      <c r="L62" s="19" t="s">
-        <v>831</v>
-      </c>
-      <c r="M62" s="19" t="s">
-        <v>832</v>
-      </c>
-      <c r="N62" s="19" t="s">
-        <v>833</v>
-      </c>
-      <c r="O62" s="19" t="s">
-        <v>834</v>
-      </c>
-      <c r="P62" s="19" t="s">
-        <v>835</v>
-      </c>
-      <c r="Q62" s="19" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="63" ht="33" spans="3:17">
+        <v>866</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>866</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>868</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="I62" s="16" t="s">
+        <v>870</v>
+      </c>
+      <c r="J62" s="16" t="s">
+        <v>871</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="O62" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="P62" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q62" s="16" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17">
       <c r="C63" s="2" t="s">
-        <v>837</v>
+        <v>877</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>839</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>840</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>841</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>842</v>
-      </c>
-      <c r="I63" s="19" t="s">
-        <v>843</v>
-      </c>
-      <c r="J63" s="19" t="s">
-        <v>844</v>
-      </c>
-      <c r="K63" s="19" t="s">
-        <v>845</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>846</v>
-      </c>
-      <c r="M63" s="19" t="s">
-        <v>847</v>
-      </c>
-      <c r="N63" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="O63" s="19" t="s">
-        <v>849</v>
-      </c>
-      <c r="P63" s="19" t="s">
-        <v>850</v>
-      </c>
-      <c r="Q63" s="19" t="s">
-        <v>851</v>
+        <v>878</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>879</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>881</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>882</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>883</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>886</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>887</v>
+      </c>
+      <c r="N63" s="16" t="s">
+        <v>888</v>
+      </c>
+      <c r="O63" s="16" t="s">
+        <v>889</v>
+      </c>
+      <c r="P63" s="16" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q63" s="16" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="2" t="s">
-        <v>852</v>
+        <v>891</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>854</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>855</v>
-      </c>
-      <c r="H64" s="19" t="s">
-        <v>856</v>
-      </c>
-      <c r="I64" s="19" t="s">
-        <v>857</v>
-      </c>
-      <c r="J64" s="19" t="s">
-        <v>858</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>859</v>
-      </c>
-      <c r="L64" s="19" t="s">
-        <v>860</v>
-      </c>
-      <c r="M64" s="19" t="s">
-        <v>861</v>
-      </c>
-      <c r="N64" s="19" t="s">
-        <v>862</v>
-      </c>
-      <c r="O64" s="19" t="s">
-        <v>863</v>
-      </c>
-      <c r="P64" s="19" t="s">
-        <v>864</v>
-      </c>
-      <c r="Q64" s="19" t="s">
-        <v>865</v>
+        <v>892</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>892</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>893</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>894</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>895</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>896</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>897</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>898</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>899</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>901</v>
+      </c>
+      <c r="O64" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="P64" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="Q64" s="16" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="2" t="s">
-        <v>866</v>
+        <v>904</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>867</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>868</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>869</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>870</v>
-      </c>
-      <c r="I65" s="19" t="s">
-        <v>871</v>
-      </c>
-      <c r="J65" s="19" t="s">
-        <v>872</v>
-      </c>
-      <c r="K65" s="19" t="s">
-        <v>873</v>
-      </c>
-      <c r="L65" s="19" t="s">
-        <v>874</v>
-      </c>
-      <c r="M65" s="19" t="s">
-        <v>875</v>
-      </c>
-      <c r="N65" s="19" t="s">
-        <v>868</v>
-      </c>
-      <c r="O65" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="P65" s="19" t="s">
-        <v>868</v>
-      </c>
-      <c r="Q65" s="19" t="s">
-        <v>877</v>
+        <v>905</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>906</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>907</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>908</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>909</v>
+      </c>
+      <c r="I65" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J65" s="16" t="s">
+        <v>910</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>911</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>913</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>914</v>
+      </c>
+      <c r="O65" s="16" t="s">
+        <v>914</v>
+      </c>
+      <c r="P65" s="16" t="s">
+        <v>915</v>
+      </c>
+      <c r="Q65" s="16" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="2" t="s">
-        <v>878</v>
+        <v>917</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>880</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>881</v>
-      </c>
-      <c r="G66" s="19" t="s">
-        <v>882</v>
-      </c>
-      <c r="H66" s="19" t="s">
-        <v>883</v>
-      </c>
-      <c r="I66" s="19" t="s">
-        <v>884</v>
-      </c>
-      <c r="J66" s="19" t="s">
-        <v>885</v>
-      </c>
-      <c r="K66" s="19" t="s">
-        <v>886</v>
-      </c>
-      <c r="L66" s="19" t="s">
-        <v>887</v>
-      </c>
-      <c r="M66" s="19" t="s">
-        <v>888</v>
-      </c>
-      <c r="N66" s="19" t="s">
-        <v>889</v>
-      </c>
-      <c r="O66" s="19" t="s">
-        <v>890</v>
-      </c>
-      <c r="P66" s="19" t="s">
-        <v>890</v>
-      </c>
-      <c r="Q66" s="19" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="67" spans="3:17">
+        <v>918</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>918</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>920</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="I66" s="16" t="s">
+        <v>922</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>925</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>926</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>927</v>
+      </c>
+      <c r="O66" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="P66" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q66" s="16" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="67" ht="34.5" spans="3:17">
       <c r="C67" s="2" t="s">
-        <v>892</v>
+        <v>931</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>893</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>894</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>895</v>
-      </c>
-      <c r="H67" s="19" t="s">
-        <v>896</v>
-      </c>
-      <c r="I67" s="19" t="s">
-        <v>897</v>
-      </c>
-      <c r="J67" s="19" t="s">
-        <v>898</v>
-      </c>
-      <c r="K67" s="19" t="s">
-        <v>899</v>
-      </c>
-      <c r="L67" s="19" t="s">
-        <v>900</v>
-      </c>
-      <c r="M67" s="19" t="s">
-        <v>901</v>
-      </c>
-      <c r="N67" s="19" t="s">
-        <v>902</v>
-      </c>
-      <c r="O67" s="19" t="s">
-        <v>903</v>
-      </c>
-      <c r="P67" s="19" t="s">
-        <v>903</v>
-      </c>
-      <c r="Q67" s="19" t="s">
-        <v>904</v>
+        <v>932</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>933</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>935</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>936</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>937</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>938</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>940</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>941</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>942</v>
+      </c>
+      <c r="O67" s="16" t="s">
+        <v>943</v>
+      </c>
+      <c r="P67" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="Q67" s="16" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="2" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>907</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>908</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>909</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>910</v>
-      </c>
-      <c r="I68" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="J68" s="19" t="s">
-        <v>911</v>
-      </c>
-      <c r="K68" s="19" t="s">
-        <v>912</v>
-      </c>
-      <c r="L68" s="19" t="s">
-        <v>913</v>
-      </c>
-      <c r="M68" s="19" t="s">
-        <v>914</v>
-      </c>
-      <c r="N68" s="19" t="s">
-        <v>915</v>
-      </c>
-      <c r="O68" s="19" t="s">
-        <v>915</v>
-      </c>
-      <c r="P68" s="19" t="s">
-        <v>916</v>
-      </c>
-      <c r="Q68" s="19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="69" spans="3:17">
+        <v>276</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="O68" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="P68" s="16" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q68" s="16" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="69" ht="51.75" spans="3:17">
       <c r="C69" s="2" t="s">
-        <v>918</v>
+        <v>948</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>919</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>920</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>921</v>
-      </c>
-      <c r="H69" s="19" t="s">
-        <v>922</v>
-      </c>
-      <c r="I69" s="19" t="s">
-        <v>923</v>
-      </c>
-      <c r="J69" s="19" t="s">
-        <v>924</v>
-      </c>
-      <c r="K69" s="19" t="s">
-        <v>925</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>926</v>
-      </c>
-      <c r="M69" s="19" t="s">
-        <v>927</v>
-      </c>
-      <c r="N69" s="19" t="s">
-        <v>928</v>
-      </c>
-      <c r="O69" s="19" t="s">
-        <v>929</v>
-      </c>
-      <c r="P69" s="19" t="s">
-        <v>930</v>
-      </c>
-      <c r="Q69" s="19" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="70" ht="33" spans="3:17">
+        <v>949</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>950</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>954</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>955</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>956</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>957</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>958</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>959</v>
+      </c>
+      <c r="O69" s="16" t="s">
+        <v>960</v>
+      </c>
+      <c r="P69" s="16" t="s">
+        <v>961</v>
+      </c>
+      <c r="Q69" s="16" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4">
       <c r="C70" s="2" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>934</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>935</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>936</v>
-      </c>
-      <c r="H70" s="19" t="s">
-        <v>937</v>
-      </c>
-      <c r="I70" s="19" t="s">
-        <v>938</v>
-      </c>
-      <c r="J70" s="19" t="s">
-        <v>939</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>940</v>
-      </c>
-      <c r="L70" s="19" t="s">
-        <v>941</v>
-      </c>
-      <c r="M70" s="19" t="s">
-        <v>942</v>
-      </c>
-      <c r="N70" s="19" t="s">
-        <v>943</v>
-      </c>
-      <c r="O70" s="19" t="s">
-        <v>944</v>
-      </c>
-      <c r="P70" s="19" t="s">
-        <v>945</v>
-      </c>
-      <c r="Q70" s="19" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="71" spans="3:17">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4">
       <c r="C71" s="2" t="s">
-        <v>947</v>
+        <v>965</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="I71" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="J71" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="K71" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="L71" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="M71" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="N71" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="O71" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="P71" s="19" t="s">
-        <v>948</v>
-      </c>
-      <c r="Q71" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="72" ht="49.5" spans="3:17">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4">
       <c r="C72" s="2" t="s">
-        <v>949</v>
+        <v>967</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>951</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>952</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>953</v>
-      </c>
-      <c r="H72" s="19" t="s">
-        <v>954</v>
-      </c>
-      <c r="I72" s="19" t="s">
-        <v>955</v>
-      </c>
-      <c r="J72" s="19" t="s">
-        <v>956</v>
-      </c>
-      <c r="K72" s="19" t="s">
-        <v>957</v>
-      </c>
-      <c r="L72" s="19" t="s">
-        <v>958</v>
-      </c>
-      <c r="M72" s="19" t="s">
-        <v>959</v>
-      </c>
-      <c r="N72" s="19" t="s">
-        <v>960</v>
-      </c>
-      <c r="O72" s="19" t="s">
-        <v>961</v>
-      </c>
-      <c r="P72" s="19" t="s">
-        <v>962</v>
-      </c>
-      <c r="Q72" s="19" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
     </row>
     <row r="73" spans="3:4">
       <c r="C73" s="2" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="74" spans="3:4">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5">
       <c r="C74" s="2" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>967</v>
+        <v>972</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="75" spans="3:4">
-      <c r="C75" s="2" t="s">
-        <v>968</v>
+      <c r="C75" s="3" t="s">
+        <v>974</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
     </row>
     <row r="76" spans="3:4">
-      <c r="C76" s="2" t="s">
-        <v>970</v>
+      <c r="C76" s="3" t="s">
+        <v>976</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5">
-      <c r="C77" s="2" t="s">
-        <v>972</v>
+        <v>977</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4">
+      <c r="C77" s="3" t="s">
+        <v>978</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>973</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
     </row>
     <row r="78" spans="3:4">
       <c r="C78" s="3" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="79" spans="3:4">
       <c r="C79" s="3" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="80" spans="3:4">
       <c r="C80" s="3" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="81" spans="3:4">
       <c r="C81" s="3" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="82" spans="3:4">
       <c r="C82" s="3" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>984</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="3:4">
       <c r="C83" s="3" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="84" spans="3:4">
       <c r="C84" s="3" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>988</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" spans="3:4">
       <c r="C85" s="3" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>202</v>
+        <v>993</v>
       </c>
     </row>
     <row r="86" spans="3:4">
       <c r="C86" s="3" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="87" spans="3:4">
       <c r="C87" s="3" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>232</v>
+        <v>997</v>
       </c>
     </row>
     <row r="88" spans="3:4">
       <c r="C88" s="3" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="89" spans="3:4">
       <c r="C89" s="3" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="90" spans="3:4">
       <c r="C90" s="3" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="91" spans="3:4">
       <c r="C91" s="3" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="92" spans="3:4">
       <c r="C92" s="3" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="93" spans="3:4">
       <c r="C93" s="3" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="94" spans="3:4">
       <c r="C94" s="3" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="95" spans="3:4">
       <c r="C95" s="3" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="96" spans="3:4">
       <c r="C96" s="3" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="97" spans="3:4">
       <c r="C97" s="3" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="98" spans="3:4">
       <c r="C98" s="3" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="99" spans="3:4">
       <c r="C99" s="3" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="100" spans="3:4">
-      <c r="C100" s="3" t="s">
-        <v>1017</v>
+      <c r="C100" s="2" t="s">
+        <v>1022</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="101" spans="3:4">
-      <c r="C101" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="102" spans="3:4">
-      <c r="C102" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="103" spans="3:4">
-      <c r="C103" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>1024</v>
       </c>
     </row>
   </sheetData>
